--- a/Current TAPPs/Solution_MC-ICP-MS_TAPP_v68.xlsx
+++ b/Current TAPPs/Solution_MC-ICP-MS_TAPP_v68.xlsx
@@ -12059,7 +12059,7 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>The measured ratio of the normalizing element is used to calculate the mass bias factor β using the chosen mass fractionation law, which is then applied to correct the target species isotope ratios assuming β_norm ≈ β_analyte.</t>
+          <t>The measured ratio of the normalizing element is used to calculate the mass bias factor β using the chosen mass fractionation law, which is then applied to correct the target species isotope ratios assuming β_norm ≈ β_species.</t>
         </is>
       </c>
       <c r="K103" s="8" t="n"/>
@@ -16361,7 +16361,7 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>Choose a listed value AND qualify it in the same cell — the detail is expected, not optional. Typically what was corrected, which analytes or phases it applied to, the method or equation used, or the source it came from. An answer the list cannot express is also valid here.</t>
+          <t>Choose a listed value AND qualify it in the same cell — the detail is expected, not optional. Typically what was corrected, which target species or phases it applied to, the method or equation used, or the source it came from. An answer the list cannot express is also valid here.</t>
         </is>
       </c>
     </row>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>ENUMERATES the channel domain — the header of the child table, not a column in it — and does so once per target species. One value per position on the instrument's selection axis — the address, not the signal. Mass, cup, line + crystal, energy-loss edge, wavenumber.</t>
+          <t>ENUMERATES the channel domain — the header of the child table, not a column in it — and does so once per target species. One value per position on the instrument's selection axis — the address, not the signal. Mass, cup, line + crystal, energy-loss edge, wavenumber. One value per chemical species determined, at whatever granularity the procedure determines it.</t>
         </is>
       </c>
     </row>
@@ -16529,7 +16529,7 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. </t>
+          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per chemical species determined, at whatever granularity the procedure determines it.</t>
         </is>
       </c>
     </row>
@@ -16607,7 +16607,11 @@
           <t>target species</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr"/>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>One value per chemical species determined, at whatever granularity the procedure determines it.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
